--- a/table_config/_tables/__beans__.xlsx
+++ b/table_config/_tables/__beans__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23540" windowHeight="14150"/>
+    <workbookView windowWidth="25880" windowHeight="11850"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -95,13 +95,19 @@
     <t>变体</t>
   </si>
   <si>
-    <t>Battle.EffectParamBase</t>
-  </si>
-  <si>
-    <t>Battle.EffectAttack</t>
-  </si>
-  <si>
-    <t>Battle.EffectHurt</t>
+    <t>Character.ParamDefine</t>
+  </si>
+  <si>
+    <t>baseValue</t>
+  </si>
+  <si>
+    <t>array#sep=|,float</t>
+  </si>
+  <si>
+    <t>format</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="28.8181818181818" customWidth="1"/>
@@ -1207,8 +1213,12 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -1216,35 +1226,31 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="5"/>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A5" s="3"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:17">
-      <c r="A6"/>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
+    <row r="6" spans="1:17">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -1258,111 +1264,129 @@
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6"/>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:17">
-      <c r="A9"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9"/>
+    <row r="7" s="1" customFormat="1" spans="1:17">
+      <c r="A7"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7"/>
     </row>
-    <row r="16" spans="1:17">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
+    <row r="10" s="1" customFormat="1" spans="1:17">
+      <c r="A10"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10"/>
     </row>
-    <row r="22" spans="2:16">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
+    <row r="17" spans="2:16">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
     </row>
-    <row r="32" spans="2:16">
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
+    <row r="23" spans="2:16">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
     </row>
-    <row r="44" spans="2:16">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
+    <row r="33" spans="2:16">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
     </row>
-    <row r="48" spans="2:16">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
+    <row r="45" spans="2:16">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="49" spans="2:16">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
